--- a/call-delivery/intake/2026-07/Branch_Central.xlsx
+++ b/call-delivery/intake/2026-07/Branch_Central.xlsx
@@ -17,11 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +53,19 @@
     </font>
     <font>
       <color rgb="006B7280"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E5AAC"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -122,7 +134,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -131,7 +143,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,6 +156,17 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I129"/>
+  <dimension ref="B2:N129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -539,12 +562,21 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>CALL DELIVERY  —  Outbound Dialing Schedule (Intake)</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>GROUP STRATEGY &amp; NOTES  (carried over from July 2026 master)</t>
         </is>
       </c>
     </row>
@@ -555,6 +587,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>No attempts on 2PAY</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -576,6 +615,11 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>NO CALLING 1PAY DURING  LAST 3 BUSINESS DAYS</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
@@ -593,8 +637,27 @@
           <t>Submitted Date:</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="16" t="n">
         <v>46220</v>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>General Strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>Monday mornings Central calls Branch AdHoc (Understaffed Branches)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>at 8a local, Central calls EST, CST &amp; PST for approxiamtely 30 mins.  MST is</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -638,13 +701,18 @@
           <t>Special Instructions</t>
         </is>
       </c>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>delayed to run with PST due to low volumes.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="18" t="n">
         <v>46204</v>
       </c>
       <c r="D10" s="10" t="n">
@@ -669,13 +737,18 @@
         </is>
       </c>
       <c r="I10" s="12" t="n"/>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>At 11:30a, Branch AdHoc &amp; Branch Special Request run for EST, CST, MST.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="18" t="n">
         <v>46205</v>
       </c>
       <c r="D11" s="10" t="n">
@@ -700,13 +773,18 @@
         </is>
       </c>
       <c r="I11" s="12" t="n"/>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>Pass should not last longer than 1 hour.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D12" s="10" t="n">
@@ -727,13 +805,18 @@
         </is>
       </c>
       <c r="I12" s="12" t="n"/>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>CENTRAL ADHOC is added to give the "extra" pass for Outbooks</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D13" s="10" t="n">
@@ -754,13 +837,18 @@
         </is>
       </c>
       <c r="I13" s="12" t="n"/>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>Central and After Hours Vendor make up to 2 Passes</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="18" t="n">
         <v>46209</v>
       </c>
       <c r="D14" s="10" t="n">
@@ -785,13 +873,18 @@
         </is>
       </c>
       <c r="I14" s="12" t="n"/>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>Lists are ordered per Special Instructions above</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D15" s="10" t="n">
@@ -816,13 +909,18 @@
         </is>
       </c>
       <c r="I15" s="12" t="n"/>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Special Req's run first, then General Population</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="18" t="n">
         <v>46210</v>
       </c>
       <c r="D16" s="10" t="n">
@@ -843,13 +941,18 @@
         </is>
       </c>
       <c r="I16" s="12" t="n"/>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>If needed, FE lists can fill gaps while waiting on recalls</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="18" t="n">
         <v>46211</v>
       </c>
       <c r="D17" s="10" t="n">
@@ -874,13 +977,18 @@
         </is>
       </c>
       <c r="I17" s="12" t="n"/>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>If FE running a Blitz, 3Pay lists can fill gaps</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="18" t="n">
         <v>46212</v>
       </c>
       <c r="D18" s="10" t="n">
@@ -905,13 +1013,18 @@
         </is>
       </c>
       <c r="I18" s="12" t="n"/>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>12:30 Afternoon pass will not include PST accounts</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="18" t="n">
         <v>46213</v>
       </c>
       <c r="D19" s="10" t="n">
@@ -936,13 +1049,18 @@
         </is>
       </c>
       <c r="I19" s="12" t="n"/>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>Night Branch Pass - Vendors start 5p CST and dials 1st Pass (NCs) on PST, then starts 2nd passes in TZ order</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D20" s="10" t="n">
@@ -969,7 +1087,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D21" s="10" t="n">
@@ -996,7 +1114,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="18" t="n">
         <v>46216</v>
       </c>
       <c r="D22" s="10" t="n">
@@ -1027,7 +1145,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D23" s="10" t="n">
@@ -1058,7 +1176,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="18" t="n">
         <v>46217</v>
       </c>
       <c r="D24" s="10" t="n">
@@ -1085,7 +1203,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="18" t="n">
         <v>46218</v>
       </c>
       <c r="D25" s="10" t="n">
@@ -1116,7 +1234,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D26" s="10" t="n">
@@ -1147,7 +1265,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D27" s="10" t="n">
@@ -1178,7 +1296,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D28" s="10" t="n">
@@ -1205,7 +1323,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D29" s="10" t="n">
@@ -1232,7 +1350,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="18" t="n">
         <v>46223</v>
       </c>
       <c r="D30" s="10" t="n">
@@ -1263,7 +1381,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D31" s="10" t="n">
@@ -1294,7 +1412,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="18" t="n">
         <v>46224</v>
       </c>
       <c r="D32" s="10" t="n">
@@ -1321,7 +1439,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="18" t="n">
         <v>46225</v>
       </c>
       <c r="D33" s="10" t="n">
@@ -1352,7 +1470,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D34" s="10" t="n">
@@ -1383,7 +1501,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" s="18" t="n">
         <v>46227</v>
       </c>
       <c r="D35" s="10" t="n">
@@ -1414,7 +1532,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D36" s="10" t="n">
@@ -1441,7 +1559,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C37" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D37" s="10" t="n">
@@ -1468,7 +1586,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="18" t="n">
         <v>46230</v>
       </c>
       <c r="D38" s="10" t="n">
@@ -1499,7 +1617,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D39" s="10" t="n">
@@ -1530,7 +1648,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" s="18" t="n">
         <v>46231</v>
       </c>
       <c r="D40" s="10" t="n">
@@ -1557,7 +1675,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="18" t="n">
         <v>46232</v>
       </c>
       <c r="D41" s="10" t="n">
@@ -1592,7 +1710,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="18" t="n">
         <v>46233</v>
       </c>
       <c r="D42" s="10" t="n">
@@ -1627,7 +1745,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="18" t="n">
         <v>46234</v>
       </c>
       <c r="D43" s="10" t="n">
@@ -1662,7 +1780,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="C44" s="18" t="n">
         <v>46220</v>
       </c>
       <c r="D44" s="10" t="n">
@@ -1693,7 +1811,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C45" s="9" t="n"/>
+      <c r="C45" s="18" t="n"/>
       <c r="D45" s="10" t="n"/>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="n"/>
@@ -1706,7 +1824,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C46" s="9" t="n"/>
+      <c r="C46" s="18" t="n"/>
       <c r="D46" s="10" t="n"/>
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
@@ -1719,7 +1837,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C47" s="9" t="n"/>
+      <c r="C47" s="18" t="n"/>
       <c r="D47" s="10" t="n"/>
       <c r="E47" s="11" t="n"/>
       <c r="F47" s="11" t="n"/>
@@ -1732,7 +1850,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C48" s="9" t="n"/>
+      <c r="C48" s="18" t="n"/>
       <c r="D48" s="10" t="n"/>
       <c r="E48" s="11" t="n"/>
       <c r="F48" s="11" t="n"/>
@@ -1745,7 +1863,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C49" s="9" t="n"/>
+      <c r="C49" s="18" t="n"/>
       <c r="D49" s="10" t="n"/>
       <c r="E49" s="11" t="n"/>
       <c r="F49" s="11" t="n"/>
@@ -1758,7 +1876,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C50" s="9" t="n"/>
+      <c r="C50" s="18" t="n"/>
       <c r="D50" s="10" t="n"/>
       <c r="E50" s="11" t="n"/>
       <c r="F50" s="11" t="n"/>
@@ -1771,7 +1889,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C51" s="9" t="n"/>
+      <c r="C51" s="18" t="n"/>
       <c r="D51" s="10" t="n"/>
       <c r="E51" s="11" t="n"/>
       <c r="F51" s="11" t="n"/>
@@ -1784,7 +1902,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C52" s="9" t="n"/>
+      <c r="C52" s="18" t="n"/>
       <c r="D52" s="10" t="n"/>
       <c r="E52" s="11" t="n"/>
       <c r="F52" s="11" t="n"/>
@@ -1797,7 +1915,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C53" s="9" t="n"/>
+      <c r="C53" s="18" t="n"/>
       <c r="D53" s="10" t="n"/>
       <c r="E53" s="11" t="n"/>
       <c r="F53" s="11" t="n"/>
@@ -1810,7 +1928,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C54" s="9" t="n"/>
+      <c r="C54" s="18" t="n"/>
       <c r="D54" s="10" t="n"/>
       <c r="E54" s="11" t="n"/>
       <c r="F54" s="11" t="n"/>
@@ -1823,7 +1941,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C55" s="9" t="n"/>
+      <c r="C55" s="18" t="n"/>
       <c r="D55" s="10" t="n"/>
       <c r="E55" s="11" t="n"/>
       <c r="F55" s="11" t="n"/>
@@ -1836,7 +1954,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C56" s="9" t="n"/>
+      <c r="C56" s="18" t="n"/>
       <c r="D56" s="10" t="n"/>
       <c r="E56" s="11" t="n"/>
       <c r="F56" s="11" t="n"/>
@@ -1849,7 +1967,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C57" s="9" t="n"/>
+      <c r="C57" s="18" t="n"/>
       <c r="D57" s="10" t="n"/>
       <c r="E57" s="11" t="n"/>
       <c r="F57" s="11" t="n"/>
@@ -1862,7 +1980,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C58" s="9" t="n"/>
+      <c r="C58" s="18" t="n"/>
       <c r="D58" s="10" t="n"/>
       <c r="E58" s="11" t="n"/>
       <c r="F58" s="11" t="n"/>
@@ -1875,7 +1993,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C59" s="9" t="n"/>
+      <c r="C59" s="18" t="n"/>
       <c r="D59" s="10" t="n"/>
       <c r="E59" s="11" t="n"/>
       <c r="F59" s="11" t="n"/>
@@ -1888,7 +2006,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C60" s="9" t="n"/>
+      <c r="C60" s="18" t="n"/>
       <c r="D60" s="10" t="n"/>
       <c r="E60" s="11" t="n"/>
       <c r="F60" s="11" t="n"/>
@@ -1901,7 +2019,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C61" s="9" t="n"/>
+      <c r="C61" s="18" t="n"/>
       <c r="D61" s="10" t="n"/>
       <c r="E61" s="11" t="n"/>
       <c r="F61" s="11" t="n"/>
@@ -1914,7 +2032,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C62" s="9" t="n"/>
+      <c r="C62" s="18" t="n"/>
       <c r="D62" s="10" t="n"/>
       <c r="E62" s="11" t="n"/>
       <c r="F62" s="11" t="n"/>
@@ -1927,7 +2045,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C63" s="9" t="n"/>
+      <c r="C63" s="18" t="n"/>
       <c r="D63" s="10" t="n"/>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="11" t="n"/>
@@ -1940,7 +2058,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C64" s="9" t="n"/>
+      <c r="C64" s="18" t="n"/>
       <c r="D64" s="10" t="n"/>
       <c r="E64" s="11" t="n"/>
       <c r="F64" s="11" t="n"/>
@@ -1953,7 +2071,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C65" s="9" t="n"/>
+      <c r="C65" s="18" t="n"/>
       <c r="D65" s="10" t="n"/>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="11" t="n"/>
@@ -1966,7 +2084,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C66" s="9" t="n"/>
+      <c r="C66" s="18" t="n"/>
       <c r="D66" s="10" t="n"/>
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="11" t="n"/>
@@ -1979,7 +2097,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C67" s="9" t="n"/>
+      <c r="C67" s="18" t="n"/>
       <c r="D67" s="10" t="n"/>
       <c r="E67" s="11" t="n"/>
       <c r="F67" s="11" t="n"/>
@@ -1992,7 +2110,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C68" s="9" t="n"/>
+      <c r="C68" s="18" t="n"/>
       <c r="D68" s="10" t="n"/>
       <c r="E68" s="11" t="n"/>
       <c r="F68" s="11" t="n"/>
@@ -2005,7 +2123,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C69" s="9" t="n"/>
+      <c r="C69" s="18" t="n"/>
       <c r="D69" s="10" t="n"/>
       <c r="E69" s="11" t="n"/>
       <c r="F69" s="11" t="n"/>
@@ -2018,7 +2136,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C70" s="9" t="n"/>
+      <c r="C70" s="18" t="n"/>
       <c r="D70" s="10" t="n"/>
       <c r="E70" s="11" t="n"/>
       <c r="F70" s="11" t="n"/>
@@ -2031,7 +2149,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C71" s="9" t="n"/>
+      <c r="C71" s="18" t="n"/>
       <c r="D71" s="10" t="n"/>
       <c r="E71" s="11" t="n"/>
       <c r="F71" s="11" t="n"/>
@@ -2044,7 +2162,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C72" s="9" t="n"/>
+      <c r="C72" s="18" t="n"/>
       <c r="D72" s="10" t="n"/>
       <c r="E72" s="11" t="n"/>
       <c r="F72" s="11" t="n"/>
@@ -2057,7 +2175,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C73" s="9" t="n"/>
+      <c r="C73" s="18" t="n"/>
       <c r="D73" s="10" t="n"/>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
@@ -2070,7 +2188,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C74" s="9" t="n"/>
+      <c r="C74" s="18" t="n"/>
       <c r="D74" s="10" t="n"/>
       <c r="E74" s="11" t="n"/>
       <c r="F74" s="11" t="n"/>
@@ -2083,7 +2201,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C75" s="9" t="n"/>
+      <c r="C75" s="18" t="n"/>
       <c r="D75" s="10" t="n"/>
       <c r="E75" s="11" t="n"/>
       <c r="F75" s="11" t="n"/>
@@ -2096,7 +2214,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C76" s="9" t="n"/>
+      <c r="C76" s="18" t="n"/>
       <c r="D76" s="10" t="n"/>
       <c r="E76" s="11" t="n"/>
       <c r="F76" s="11" t="n"/>
@@ -2109,7 +2227,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C77" s="9" t="n"/>
+      <c r="C77" s="18" t="n"/>
       <c r="D77" s="10" t="n"/>
       <c r="E77" s="11" t="n"/>
       <c r="F77" s="11" t="n"/>
@@ -2122,7 +2240,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C78" s="9" t="n"/>
+      <c r="C78" s="18" t="n"/>
       <c r="D78" s="10" t="n"/>
       <c r="E78" s="11" t="n"/>
       <c r="F78" s="11" t="n"/>
@@ -2135,7 +2253,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C79" s="9" t="n"/>
+      <c r="C79" s="18" t="n"/>
       <c r="D79" s="10" t="n"/>
       <c r="E79" s="11" t="n"/>
       <c r="F79" s="11" t="n"/>
@@ -2148,7 +2266,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C80" s="9" t="n"/>
+      <c r="C80" s="18" t="n"/>
       <c r="D80" s="10" t="n"/>
       <c r="E80" s="11" t="n"/>
       <c r="F80" s="11" t="n"/>
@@ -2161,7 +2279,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C81" s="9" t="n"/>
+      <c r="C81" s="18" t="n"/>
       <c r="D81" s="10" t="n"/>
       <c r="E81" s="11" t="n"/>
       <c r="F81" s="11" t="n"/>
@@ -2174,7 +2292,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C82" s="9" t="n"/>
+      <c r="C82" s="18" t="n"/>
       <c r="D82" s="10" t="n"/>
       <c r="E82" s="11" t="n"/>
       <c r="F82" s="11" t="n"/>
@@ -2187,7 +2305,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C83" s="9" t="n"/>
+      <c r="C83" s="18" t="n"/>
       <c r="D83" s="10" t="n"/>
       <c r="E83" s="11" t="n"/>
       <c r="F83" s="11" t="n"/>
@@ -2200,7 +2318,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C84" s="9" t="n"/>
+      <c r="C84" s="18" t="n"/>
       <c r="D84" s="10" t="n"/>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
@@ -2213,7 +2331,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C85" s="9" t="n"/>
+      <c r="C85" s="18" t="n"/>
       <c r="D85" s="10" t="n"/>
       <c r="E85" s="11" t="n"/>
       <c r="F85" s="11" t="n"/>
@@ -2226,7 +2344,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C86" s="9" t="n"/>
+      <c r="C86" s="18" t="n"/>
       <c r="D86" s="10" t="n"/>
       <c r="E86" s="11" t="n"/>
       <c r="F86" s="11" t="n"/>
@@ -2239,7 +2357,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C87" s="9" t="n"/>
+      <c r="C87" s="18" t="n"/>
       <c r="D87" s="10" t="n"/>
       <c r="E87" s="11" t="n"/>
       <c r="F87" s="11" t="n"/>
@@ -2252,7 +2370,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C88" s="9" t="n"/>
+      <c r="C88" s="18" t="n"/>
       <c r="D88" s="10" t="n"/>
       <c r="E88" s="11" t="n"/>
       <c r="F88" s="11" t="n"/>
@@ -2265,7 +2383,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C89" s="9" t="n"/>
+      <c r="C89" s="18" t="n"/>
       <c r="D89" s="10" t="n"/>
       <c r="E89" s="11" t="n"/>
       <c r="F89" s="11" t="n"/>
@@ -2278,7 +2396,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C90" s="9" t="n"/>
+      <c r="C90" s="18" t="n"/>
       <c r="D90" s="10" t="n"/>
       <c r="E90" s="11" t="n"/>
       <c r="F90" s="11" t="n"/>
@@ -2291,7 +2409,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C91" s="9" t="n"/>
+      <c r="C91" s="18" t="n"/>
       <c r="D91" s="10" t="n"/>
       <c r="E91" s="11" t="n"/>
       <c r="F91" s="11" t="n"/>
@@ -2304,7 +2422,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C92" s="9" t="n"/>
+      <c r="C92" s="18" t="n"/>
       <c r="D92" s="10" t="n"/>
       <c r="E92" s="11" t="n"/>
       <c r="F92" s="11" t="n"/>
@@ -2317,7 +2435,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C93" s="9" t="n"/>
+      <c r="C93" s="18" t="n"/>
       <c r="D93" s="10" t="n"/>
       <c r="E93" s="11" t="n"/>
       <c r="F93" s="11" t="n"/>
@@ -2330,7 +2448,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C94" s="9" t="n"/>
+      <c r="C94" s="18" t="n"/>
       <c r="D94" s="10" t="n"/>
       <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
@@ -2343,7 +2461,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C95" s="9" t="n"/>
+      <c r="C95" s="18" t="n"/>
       <c r="D95" s="10" t="n"/>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="11" t="n"/>
@@ -2356,7 +2474,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C96" s="9" t="n"/>
+      <c r="C96" s="18" t="n"/>
       <c r="D96" s="10" t="n"/>
       <c r="E96" s="11" t="n"/>
       <c r="F96" s="11" t="n"/>
@@ -2369,7 +2487,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C97" s="9" t="n"/>
+      <c r="C97" s="18" t="n"/>
       <c r="D97" s="10" t="n"/>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
@@ -2382,7 +2500,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C98" s="9" t="n"/>
+      <c r="C98" s="18" t="n"/>
       <c r="D98" s="10" t="n"/>
       <c r="E98" s="11" t="n"/>
       <c r="F98" s="11" t="n"/>
@@ -2395,7 +2513,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C99" s="9" t="n"/>
+      <c r="C99" s="18" t="n"/>
       <c r="D99" s="10" t="n"/>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
@@ -2408,7 +2526,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C100" s="9" t="n"/>
+      <c r="C100" s="18" t="n"/>
       <c r="D100" s="10" t="n"/>
       <c r="E100" s="11" t="n"/>
       <c r="F100" s="11" t="n"/>
@@ -2421,7 +2539,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C101" s="9" t="n"/>
+      <c r="C101" s="18" t="n"/>
       <c r="D101" s="10" t="n"/>
       <c r="E101" s="11" t="n"/>
       <c r="F101" s="11" t="n"/>
@@ -2434,7 +2552,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C102" s="9" t="n"/>
+      <c r="C102" s="18" t="n"/>
       <c r="D102" s="10" t="n"/>
       <c r="E102" s="11" t="n"/>
       <c r="F102" s="11" t="n"/>
@@ -2447,7 +2565,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C103" s="9" t="n"/>
+      <c r="C103" s="18" t="n"/>
       <c r="D103" s="10" t="n"/>
       <c r="E103" s="11" t="n"/>
       <c r="F103" s="11" t="n"/>
@@ -2460,7 +2578,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C104" s="9" t="n"/>
+      <c r="C104" s="18" t="n"/>
       <c r="D104" s="10" t="n"/>
       <c r="E104" s="11" t="n"/>
       <c r="F104" s="11" t="n"/>
@@ -2473,7 +2591,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C105" s="9" t="n"/>
+      <c r="C105" s="18" t="n"/>
       <c r="D105" s="10" t="n"/>
       <c r="E105" s="11" t="n"/>
       <c r="F105" s="11" t="n"/>
@@ -2486,7 +2604,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C106" s="9" t="n"/>
+      <c r="C106" s="18" t="n"/>
       <c r="D106" s="10" t="n"/>
       <c r="E106" s="11" t="n"/>
       <c r="F106" s="11" t="n"/>
@@ -2499,7 +2617,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C107" s="9" t="n"/>
+      <c r="C107" s="18" t="n"/>
       <c r="D107" s="10" t="n"/>
       <c r="E107" s="11" t="n"/>
       <c r="F107" s="11" t="n"/>
@@ -2512,7 +2630,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C108" s="9" t="n"/>
+      <c r="C108" s="18" t="n"/>
       <c r="D108" s="10" t="n"/>
       <c r="E108" s="11" t="n"/>
       <c r="F108" s="11" t="n"/>
@@ -2525,7 +2643,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C109" s="9" t="n"/>
+      <c r="C109" s="18" t="n"/>
       <c r="D109" s="10" t="n"/>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
@@ -2538,7 +2656,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C110" s="9" t="n"/>
+      <c r="C110" s="18" t="n"/>
       <c r="D110" s="10" t="n"/>
       <c r="E110" s="11" t="n"/>
       <c r="F110" s="11" t="n"/>
@@ -2551,7 +2669,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C111" s="9" t="n"/>
+      <c r="C111" s="18" t="n"/>
       <c r="D111" s="10" t="n"/>
       <c r="E111" s="11" t="n"/>
       <c r="F111" s="11" t="n"/>
@@ -2564,7 +2682,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C112" s="9" t="n"/>
+      <c r="C112" s="18" t="n"/>
       <c r="D112" s="10" t="n"/>
       <c r="E112" s="11" t="n"/>
       <c r="F112" s="11" t="n"/>
@@ -2577,7 +2695,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C113" s="9" t="n"/>
+      <c r="C113" s="18" t="n"/>
       <c r="D113" s="10" t="n"/>
       <c r="E113" s="11" t="n"/>
       <c r="F113" s="11" t="n"/>
@@ -2590,7 +2708,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C114" s="9" t="n"/>
+      <c r="C114" s="18" t="n"/>
       <c r="D114" s="10" t="n"/>
       <c r="E114" s="11" t="n"/>
       <c r="F114" s="11" t="n"/>
@@ -2603,7 +2721,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C115" s="9" t="n"/>
+      <c r="C115" s="18" t="n"/>
       <c r="D115" s="10" t="n"/>
       <c r="E115" s="11" t="n"/>
       <c r="F115" s="11" t="n"/>
@@ -2616,7 +2734,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C116" s="9" t="n"/>
+      <c r="C116" s="18" t="n"/>
       <c r="D116" s="10" t="n"/>
       <c r="E116" s="11" t="n"/>
       <c r="F116" s="11" t="n"/>
@@ -2629,7 +2747,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C117" s="9" t="n"/>
+      <c r="C117" s="18" t="n"/>
       <c r="D117" s="10" t="n"/>
       <c r="E117" s="11" t="n"/>
       <c r="F117" s="11" t="n"/>
@@ -2642,7 +2760,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C118" s="9" t="n"/>
+      <c r="C118" s="18" t="n"/>
       <c r="D118" s="10" t="n"/>
       <c r="E118" s="11" t="n"/>
       <c r="F118" s="11" t="n"/>
@@ -2655,7 +2773,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C119" s="9" t="n"/>
+      <c r="C119" s="18" t="n"/>
       <c r="D119" s="10" t="n"/>
       <c r="E119" s="11" t="n"/>
       <c r="F119" s="11" t="n"/>
@@ -2668,7 +2786,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C120" s="9" t="n"/>
+      <c r="C120" s="18" t="n"/>
       <c r="D120" s="10" t="n"/>
       <c r="E120" s="11" t="n"/>
       <c r="F120" s="11" t="n"/>
@@ -2681,7 +2799,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C121" s="9" t="n"/>
+      <c r="C121" s="18" t="n"/>
       <c r="D121" s="10" t="n"/>
       <c r="E121" s="11" t="n"/>
       <c r="F121" s="11" t="n"/>
@@ -2694,7 +2812,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C122" s="9" t="n"/>
+      <c r="C122" s="18" t="n"/>
       <c r="D122" s="10" t="n"/>
       <c r="E122" s="11" t="n"/>
       <c r="F122" s="11" t="n"/>
@@ -2707,7 +2825,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C123" s="9" t="n"/>
+      <c r="C123" s="18" t="n"/>
       <c r="D123" s="10" t="n"/>
       <c r="E123" s="11" t="n"/>
       <c r="F123" s="11" t="n"/>
@@ -2720,7 +2838,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C124" s="9" t="n"/>
+      <c r="C124" s="18" t="n"/>
       <c r="D124" s="10" t="n"/>
       <c r="E124" s="11" t="n"/>
       <c r="F124" s="11" t="n"/>
@@ -2733,7 +2851,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C125" s="9" t="n"/>
+      <c r="C125" s="18" t="n"/>
       <c r="D125" s="10" t="n"/>
       <c r="E125" s="11" t="n"/>
       <c r="F125" s="11" t="n"/>
@@ -2746,7 +2864,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C126" s="9" t="n"/>
+      <c r="C126" s="18" t="n"/>
       <c r="D126" s="10" t="n"/>
       <c r="E126" s="11" t="n"/>
       <c r="F126" s="11" t="n"/>
@@ -2759,7 +2877,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C127" s="9" t="n"/>
+      <c r="C127" s="18" t="n"/>
       <c r="D127" s="10" t="n"/>
       <c r="E127" s="11" t="n"/>
       <c r="F127" s="11" t="n"/>
@@ -2772,7 +2890,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C128" s="9" t="n"/>
+      <c r="C128" s="18" t="n"/>
       <c r="D128" s="10" t="n"/>
       <c r="E128" s="11" t="n"/>
       <c r="F128" s="11" t="n"/>
@@ -2785,7 +2903,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C129" s="9" t="n"/>
+      <c r="C129" s="18" t="n"/>
       <c r="D129" s="10" t="n"/>
       <c r="E129" s="11" t="n"/>
       <c r="F129" s="11" t="n"/>
@@ -2794,9 +2912,26 @@
       <c r="I129" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="19">
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="K17:N17"/>
     <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="K18:N18"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K2:N2"/>
   </mergeCells>
   <dataValidations count="7">
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/call-delivery/intake/2026-07/Branch_Central.xlsx
+++ b/call-delivery/intake/2026-07/Branch_Central.xlsx
@@ -1780,30 +1780,12 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C44" s="18" t="n">
-        <v>46220</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>0.5208333333333334</v>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>E-C</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>1s &amp; Slow</t>
-        </is>
-      </c>
+      <c r="C44" s="18" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="11" t="n"/>
       <c r="I44" s="12" t="n"/>
     </row>
     <row r="45">
